--- a/4_ethics_and_licensing/software_data_inventory.xlsx
+++ b/4_ethics_and_licensing/software_data_inventory.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marko\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94df54f4ae1584ba/Documents/Uni/Year 2/Team project/Team-Project-1/4_ethics_and_licensing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B17A9B1E-7EBE-4D87-B469-EAA62671C9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{B17A9B1E-7EBE-4D87-B469-EAA62671C9D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0B6AD05E-D4A3-4839-BF7C-6FADC07F412F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="83">
   <si>
     <t>Category</t>
   </si>
@@ -251,6 +251,24 @@
   </si>
   <si>
     <t>Java</t>
+  </si>
+  <si>
+    <t>Productino</t>
+  </si>
+  <si>
+    <t>PostgreSQL JDBC Driver</t>
+  </si>
+  <si>
+    <t>org.postgresql</t>
+  </si>
+  <si>
+    <t>postgresql</t>
+  </si>
+  <si>
+    <t>BSD 2-Clause</t>
+  </si>
+  <si>
+    <t>Production on DB driver for Render and PostgreSQL database</t>
   </si>
 </sst>
 </file>
@@ -613,19 +631,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.08984375" customWidth="1"/>
-    <col min="2" max="2" width="28.453125" customWidth="1"/>
-    <col min="3" max="3" width="23.90625" customWidth="1"/>
-    <col min="4" max="4" width="20.7265625" customWidth="1"/>
-    <col min="5" max="5" width="22.1796875" customWidth="1"/>
-    <col min="6" max="6" width="12.08984375" customWidth="1"/>
-    <col min="7" max="7" width="17.26953125" customWidth="1"/>
+    <col min="1" max="1" width="36.109375" customWidth="1"/>
+    <col min="2" max="2" width="28.44140625" customWidth="1"/>
+    <col min="3" max="3" width="23.88671875" customWidth="1"/>
+    <col min="4" max="4" width="20.77734375" customWidth="1"/>
+    <col min="5" max="5" width="22.21875" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -651,7 +669,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -674,7 +692,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -700,7 +718,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -726,7 +744,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -752,7 +770,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -778,7 +796,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -804,7 +822,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -830,7 +848,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -856,7 +874,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>41</v>
       </c>
@@ -882,7 +900,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>41</v>
       </c>
@@ -908,7 +926,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>57</v>
       </c>
@@ -931,7 +949,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>57</v>
       </c>
@@ -954,7 +972,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -977,7 +995,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>57</v>
       </c>
@@ -1000,7 +1018,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -1012,6 +1030,32 @@
       </c>
       <c r="H16" t="s">
         <v>75</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>77</v>
+      </c>
+      <c r="B17" t="s">
+        <v>78</v>
+      </c>
+      <c r="C17" t="s">
+        <v>79</v>
+      </c>
+      <c r="D17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" t="s">
+        <v>28</v>
+      </c>
+      <c r="G17" t="s">
+        <v>81</v>
+      </c>
+      <c r="H17" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
